--- a/artfynd/A 43991-2023 artfynd.xlsx
+++ b/artfynd/A 43991-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118035343</v>
       </c>
       <c r="B2" t="n">
-        <v>57440</v>
+        <v>57441</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 43991-2023 artfynd.xlsx
+++ b/artfynd/A 43991-2023 artfynd.xlsx
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119692781</v>
+        <v>119692301</v>
       </c>
       <c r="B4" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,21 +917,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>398718</v>
+        <v>398576</v>
       </c>
       <c r="R4" t="n">
-        <v>6966155</v>
+        <v>6966337</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -976,7 +976,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119692301</v>
+        <v>119692781</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
+        <v>90562</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,21 +1029,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>398576</v>
+        <v>398718</v>
       </c>
       <c r="R5" t="n">
-        <v>6966337</v>
+        <v>6966155</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1349,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119828239</v>
+        <v>119828236</v>
       </c>
       <c r="B8" t="n">
-        <v>91883</v>
+        <v>91834</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5448</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>398588</v>
+        <v>398866</v>
       </c>
       <c r="R8" t="n">
-        <v>6966336</v>
+        <v>6965848</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1561,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119828236</v>
+        <v>119828239</v>
       </c>
       <c r="B10" t="n">
-        <v>91834</v>
+        <v>91883</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4362</v>
+        <v>5448</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>398866</v>
+        <v>398588</v>
       </c>
       <c r="R10" t="n">
-        <v>6965848</v>
+        <v>6966336</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 43991-2023 artfynd.xlsx
+++ b/artfynd/A 43991-2023 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119691276</v>
+        <v>119692781</v>
       </c>
       <c r="B3" t="n">
-        <v>90558</v>
+        <v>90562</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,21 +805,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>398691</v>
+        <v>398718</v>
       </c>
       <c r="R3" t="n">
-        <v>6966303</v>
+        <v>6966155</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,7 +901,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119692301</v>
+        <v>119691411</v>
       </c>
       <c r="B4" t="n">
         <v>90580</v>
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>398576</v>
+        <v>398694</v>
       </c>
       <c r="R4" t="n">
-        <v>6966337</v>
+        <v>6966313</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -976,7 +976,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119692781</v>
+        <v>119690843</v>
       </c>
       <c r="B5" t="n">
-        <v>90562</v>
+        <v>79636</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,25 +1025,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>398718</v>
+        <v>398871</v>
       </c>
       <c r="R5" t="n">
-        <v>6966155</v>
+        <v>6966019</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119691411</v>
+        <v>119691276</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
+        <v>90558</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,21 +1141,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>398694</v>
+        <v>398691</v>
       </c>
       <c r="R6" t="n">
-        <v>6966313</v>
+        <v>6966303</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119690843</v>
+        <v>119692301</v>
       </c>
       <c r="B7" t="n">
-        <v>79636</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1249,25 +1249,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>398871</v>
+        <v>398576</v>
       </c>
       <c r="R7" t="n">
-        <v>6966019</v>
+        <v>6966337</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 43991-2023 artfynd.xlsx
+++ b/artfynd/A 43991-2023 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119692781</v>
+        <v>119691276</v>
       </c>
       <c r="B3" t="n">
-        <v>90562</v>
+        <v>90558</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,21 +805,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>398718</v>
+        <v>398691</v>
       </c>
       <c r="R3" t="n">
-        <v>6966155</v>
+        <v>6966303</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119690843</v>
+        <v>119692781</v>
       </c>
       <c r="B5" t="n">
-        <v>79636</v>
+        <v>90562</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,25 +1025,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>398871</v>
+        <v>398718</v>
       </c>
       <c r="R5" t="n">
-        <v>6966019</v>
+        <v>6966155</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119691276</v>
+        <v>119692301</v>
       </c>
       <c r="B6" t="n">
-        <v>90558</v>
+        <v>90580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,21 +1141,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>398691</v>
+        <v>398576</v>
       </c>
       <c r="R6" t="n">
-        <v>6966303</v>
+        <v>6966337</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,10 +1237,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119692301</v>
+        <v>119690843</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>79636</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1249,25 +1249,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>398576</v>
+        <v>398871</v>
       </c>
       <c r="R7" t="n">
-        <v>6966337</v>
+        <v>6966019</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 43991-2023 artfynd.xlsx
+++ b/artfynd/A 43991-2023 artfynd.xlsx
@@ -1349,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119828236</v>
+        <v>119828239</v>
       </c>
       <c r="B8" t="n">
-        <v>91834</v>
+        <v>91901</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>5448</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>398866</v>
+        <v>398588</v>
       </c>
       <c r="R8" t="n">
-        <v>6965848</v>
+        <v>6966336</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1458,7 +1458,7 @@
         <v>119828240</v>
       </c>
       <c r="B9" t="n">
-        <v>79608</v>
+        <v>79624</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1561,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119828239</v>
+        <v>119828236</v>
       </c>
       <c r="B10" t="n">
-        <v>91883</v>
+        <v>91852</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5448</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>398588</v>
+        <v>398866</v>
       </c>
       <c r="R10" t="n">
-        <v>6966336</v>
+        <v>6965848</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 43991-2023 artfynd.xlsx
+++ b/artfynd/A 43991-2023 artfynd.xlsx
@@ -1349,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119828239</v>
+        <v>119828240</v>
       </c>
       <c r="B8" t="n">
-        <v>91901</v>
+        <v>79624</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5448</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>398588</v>
+        <v>398727</v>
       </c>
       <c r="R8" t="n">
-        <v>6966336</v>
+        <v>6966199</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119828240</v>
+        <v>119828236</v>
       </c>
       <c r="B9" t="n">
-        <v>79624</v>
+        <v>91852</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,21 +1471,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1498,10 +1498,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>398727</v>
+        <v>398866</v>
       </c>
       <c r="R9" t="n">
-        <v>6966199</v>
+        <v>6965848</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1561,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119828236</v>
+        <v>119828239</v>
       </c>
       <c r="B10" t="n">
-        <v>91852</v>
+        <v>91901</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4362</v>
+        <v>5448</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>398866</v>
+        <v>398588</v>
       </c>
       <c r="R10" t="n">
-        <v>6965848</v>
+        <v>6966336</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 43991-2023 artfynd.xlsx
+++ b/artfynd/A 43991-2023 artfynd.xlsx
@@ -1349,10 +1349,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119828240</v>
+        <v>119828236</v>
       </c>
       <c r="B8" t="n">
-        <v>79624</v>
+        <v>91852</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>398727</v>
+        <v>398866</v>
       </c>
       <c r="R8" t="n">
-        <v>6966199</v>
+        <v>6965848</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119828236</v>
+        <v>119828239</v>
       </c>
       <c r="B9" t="n">
-        <v>91852</v>
+        <v>91901</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,21 +1471,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>5448</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1498,10 +1498,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>398866</v>
+        <v>398588</v>
       </c>
       <c r="R9" t="n">
-        <v>6965848</v>
+        <v>6966336</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1561,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119828239</v>
+        <v>119828240</v>
       </c>
       <c r="B10" t="n">
-        <v>91901</v>
+        <v>79624</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5448</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>398588</v>
+        <v>398727</v>
       </c>
       <c r="R10" t="n">
-        <v>6966336</v>
+        <v>6966199</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 43991-2023 artfynd.xlsx
+++ b/artfynd/A 43991-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118035343</v>
+        <v>119691276</v>
       </c>
       <c r="B2" t="n">
-        <v>57443</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,49 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>sikåsen, Storsjö, Hjd</t>
+          <t>Småtjärnarna, Småtjärnarna, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>398884</v>
+        <v>398691</v>
       </c>
       <c r="R2" t="n">
-        <v>6965966</v>
+        <v>6966303</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,12 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,27 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kent Moén</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kent Moén</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119691276</v>
+        <v>119692781</v>
       </c>
       <c r="B3" t="n">
-        <v>90558</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>398691</v>
+        <v>398718</v>
       </c>
       <c r="R3" t="n">
-        <v>6966303</v>
+        <v>6966155</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -864,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119691411</v>
+        <v>119828240</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,37 +900,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Småtjärnarna, Hjd</t>
+          <t>Småtjärnarna, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>398694</v>
+        <v>398727</v>
       </c>
       <c r="R4" t="n">
-        <v>6966313</v>
+        <v>6966199</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,27 +960,18 @@
           <t>2024-09-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>18:55</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-11</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>18:55</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1013,15 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119692781</v>
+        <v>119828236</v>
       </c>
       <c r="B5" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1029,37 +1001,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Småtjärnarna, Hjd</t>
+          <t>Småtjärnarna, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>398718</v>
+        <v>398866</v>
       </c>
       <c r="R5" t="n">
-        <v>6966155</v>
+        <v>6965848</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,27 +1061,18 @@
           <t>2024-09-11</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>19:54</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-11</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>19:54</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1125,15 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119692301</v>
+        <v>119828239</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1141,37 +1102,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>5448</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Småtjärnarna, Hjd</t>
+          <t>Småtjärnarna, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>398576</v>
+        <v>398588</v>
       </c>
       <c r="R6" t="n">
-        <v>6966337</v>
+        <v>6966336</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,27 +1162,18 @@
           <t>2024-09-11</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>19:36</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-11</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>19:36</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1240,12 +1195,7 @@
         <v>119690843</v>
       </c>
       <c r="B7" t="n">
-        <v>79636</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,15 +1299,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119828236</v>
+        <v>118035343</v>
       </c>
       <c r="B8" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1365,37 +1310,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Småtjärnarna, Hjd</t>
+          <t>sikåsen, Storsjö, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>398866</v>
+        <v>398884</v>
       </c>
       <c r="R8" t="n">
-        <v>6965848</v>
+        <v>6965966</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,12 +1376,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-11</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1436,234 +1390,21 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Kent Moén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Kent Moén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>119828239</v>
-      </c>
-      <c r="B9" t="n">
-        <v>91901</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>5448</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Svartvit taggsvamp</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Phellodon connatus</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Småtjärnarna, Hjd</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>398588</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6966336</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Erik Wilhelmsson</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Erik Wilhelmsson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>119828240</v>
-      </c>
-      <c r="B10" t="n">
-        <v>79624</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>2081</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Skrovellav</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Småtjärnarna, Hjd</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>398727</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6966199</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Storsjö</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Erik Wilhelmsson</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Erik Wilhelmsson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43991-2023 artfynd.xlsx
+++ b/artfynd/A 43991-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119691276</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119692781</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119828240</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119828236</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1189,6 +1214,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119828239</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1296,6 +1326,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119690843</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1405,8 +1440,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118035343</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>